--- a/build/assets/Audio/lesson_vo_manifest.xlsx
+++ b/build/assets/Audio/lesson_vo_manifest.xlsx
@@ -43,17 +43,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,14 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -535,49 +526,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Start screen</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Start screen</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>vo_landing</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>नमस्ते दोस्तो! आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>greeting and what the lesson is about</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Start screen opens, before the play button</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>SYNTHESISED - record a human take of the line in column D</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -603,7 +594,7 @@
           <t>vo_pt_tutorial</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>(shared kit recording - already delivered, nothing to script or re-record)</t>
         </is>
@@ -650,7 +641,7 @@
           <t>vo_line_l2</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>चूहे ने चार चने चबाए।</t>
         </is>
@@ -671,7 +662,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -701,7 +692,7 @@
           <t>vo_ltr_ch</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>च</t>
         </is>
@@ -722,7 +713,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -752,7 +743,7 @@
           <t>vo_t3_explain</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
@@ -769,7 +760,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -799,7 +790,7 @@
           <t>vo_t4_prompt</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
@@ -816,7 +807,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>6.72</v>
+        <v>6.64</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -846,7 +837,7 @@
           <t>vo_w_chuha</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>चूहा</t>
         </is>
@@ -867,7 +858,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -897,7 +888,7 @@
           <t>vo_snd_ch</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>च से चम्मच।</t>
         </is>
@@ -918,7 +909,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -948,7 +939,7 @@
           <t>vo_line_l3</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>मेरे मामा मीठी मलाई लाए।</t>
         </is>
@@ -965,7 +956,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -995,7 +986,7 @@
           <t>vo_ltr_m</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>म</t>
         </is>
@@ -1016,7 +1007,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1046,7 +1037,7 @@
           <t>vo_t5_explain</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
@@ -1063,7 +1054,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>8.119999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1093,7 +1084,7 @@
           <t>vo_t6_prompt</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>7.72</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1140,7 +1131,7 @@
           <t>vo_w_muli</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>मूली</t>
         </is>
@@ -1161,7 +1152,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1191,7 +1182,7 @@
           <t>vo_snd_m</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>म से मछली।</t>
         </is>
@@ -1212,7 +1203,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1242,7 +1233,7 @@
           <t>vo_line_l1</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>पीतल के पतीले में पपीता पीला-पीला।</t>
         </is>
@@ -1259,7 +1250,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1289,7 +1280,7 @@
           <t>vo_ltr_p</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>प</t>
         </is>
@@ -1306,7 +1297,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.84</v>
+        <v>1.12</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1336,7 +1327,7 @@
           <t>vo_t1_explain</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
@@ -1353,7 +1344,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>8.56</v>
+        <v>8.68</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1383,7 +1374,7 @@
           <t>vo_t2_prompt</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
@@ -1400,7 +1391,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>7.56</v>
+        <v>7.28</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1430,7 +1421,7 @@
           <t>vo_w_papita</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>पपीता</t>
         </is>
@@ -1451,7 +1442,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1481,7 +1472,7 @@
           <t>vo_snd_p</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -1502,7 +1493,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1511,49 +1502,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Page 7</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>vo_g2_prompt</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>page instruction</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Page opens</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1570,7 @@
           <t>vo_snd_p</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -1600,7 +1591,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1630,7 +1621,7 @@
           <t>vo_w_papita</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>पपीता</t>
         </is>
@@ -1651,7 +1642,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1681,7 +1672,7 @@
           <t>vo_w_kela</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>केला</t>
         </is>
@@ -1702,7 +1693,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1732,7 +1723,7 @@
           <t>vo_w_patang</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>पतंग</t>
         </is>
@@ -1753,7 +1744,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1783,7 +1774,7 @@
           <t>vo_w_aam</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>आम</t>
         </is>
@@ -1804,7 +1795,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1834,7 +1825,7 @@
           <t>vo_g2_more</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>एक और प वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -1851,7 +1842,7 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1881,7 +1872,7 @@
           <t>vo_g2_try</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>इस शब्द की शुरुआत में प की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -1898,7 +1889,7 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>5.12</v>
+        <v>5.56</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1928,7 +1919,7 @@
           <t>vo_g2_hint</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>हर शब्द को ध्यान से देखिए और सुनिए। किस शब्द में प की आवाज़ आ रही है?</t>
         </is>
@@ -1945,7 +1936,7 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>6.48</v>
+        <v>5.88</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1954,137 +1945,143 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Page 7</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>vo_g2_h1</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Hint 1</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>After the 1st wrong try</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Page 7</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>vo_g2_h2</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Hint 2</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>After the 2nd wrong try</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Page 7</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" t="n">
         <v>12</v>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>vo_g2_h3</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Hint 3</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>After the 3rd wrong try</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2107,7 @@
           <t>vo_g2_reveal</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें प की आवाज़ है।</t>
         </is>
@@ -2127,7 +2124,7 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2157,7 +2154,7 @@
           <t>vo_g2_done</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>शाबाश! तुमने प की आवाज़ वाले सारे शब्द खोज लिए।</t>
         </is>
@@ -2174,7 +2171,7 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>5.24</v>
+        <v>5.56</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2183,49 +2180,49 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Page 8</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>vo_p1_prompt</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>page instruction</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Page opens</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2248,7 @@
           <t>vo_snd_m</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>म से मछली।</t>
         </is>
@@ -2272,7 +2269,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2302,7 +2299,7 @@
           <t>vo_w_mama</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>मामा</t>
         </is>
@@ -2349,7 +2346,7 @@
           <t>vo_w_chidiya</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>चिड़िया</t>
         </is>
@@ -2366,7 +2363,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2396,7 +2393,7 @@
           <t>vo_w_muli</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>मूली</t>
         </is>
@@ -2417,7 +2414,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2447,7 +2444,7 @@
           <t>vo_w_laddu</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>लड्डू</t>
         </is>
@@ -2464,7 +2461,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2494,7 +2491,7 @@
           <t>vo_p1_more</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>एक और म वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -2511,7 +2508,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2541,7 +2538,7 @@
           <t>vo_p1_try</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -2558,7 +2555,7 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>5.08</v>
+        <v>6.16</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2588,7 +2585,7 @@
           <t>vo_p1_hint</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
         </is>
@@ -2605,7 +2602,7 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>4.96</v>
+        <v>4.48</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2614,137 +2611,143 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Page 8</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" t="n">
         <v>10</v>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>vo_p1_h1</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Hint 1</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>After the 1st wrong try</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Page 8</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" t="n">
         <v>11</v>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>vo_p1_h2</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Hint 2</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>After the 2nd wrong try</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Page 8</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" t="n">
         <v>12</v>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>vo_p1_h3</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Hint 3</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>After the 3rd wrong try</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2773,7 @@
           <t>vo_p1_reveal</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें म की आवाज़ है।</t>
         </is>
@@ -2787,7 +2790,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2817,7 +2820,7 @@
           <t>vo_p1_done</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
         </is>
@@ -2834,7 +2837,7 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>4.24</v>
+        <v>4.48</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2843,49 +2846,49 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Page 9</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>vo_p7_prompt</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>page instruction</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Page opens</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2914,7 @@
           <t>vo_snd_ch</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>च से चम्मच।</t>
         </is>
@@ -2932,7 +2935,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -2962,7 +2965,7 @@
           <t>vo_w_chand</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>चाँद</t>
         </is>
@@ -2983,7 +2986,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3013,7 +3016,7 @@
           <t>vo_w_mala</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>माला</t>
         </is>
@@ -3034,7 +3037,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3064,7 +3067,7 @@
           <t>vo_w_chashma</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>चश्मा</t>
         </is>
@@ -3111,7 +3114,7 @@
           <t>vo_w_laal</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>लाल</t>
         </is>
@@ -3132,7 +3135,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3162,7 +3165,7 @@
           <t>vo_p7_more</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -3179,7 +3182,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3209,7 +3212,7 @@
           <t>vo_p7_try</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -3226,7 +3229,7 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>4.84</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3256,7 +3259,7 @@
           <t>vo_p7_hint</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
@@ -3273,146 +3276,152 @@
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Page 9</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tap every word with that sound</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>vo_p7_h1</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hint 1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>After the 1st wrong try</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
         <v>6.28</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Page 9</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h1</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>Hint 1</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>After the 1st wrong try</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr"/>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="D63" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>vo_p7_h2</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hint 2</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>After the 2nd wrong try</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Page 9</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Tap every word with that sound</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h2</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>Hint 2</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>After the 2nd wrong try</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Tap every word with that sound</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" t="n">
         <v>12</v>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>vo_p7_h3</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Hint 3</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>After the 3rd wrong try</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3447,7 @@
           <t>vo_p7_reveal</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
@@ -3455,7 +3464,7 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3485,7 +3494,7 @@
           <t>vo_p7_done</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
@@ -3502,7 +3511,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3532,7 +3541,7 @@
           <t>vo_line_l2</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>चूहे ने चार चने चबाए।</t>
         </is>
@@ -3553,7 +3562,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3583,7 +3592,7 @@
           <t>vo_g3_prompt</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
         </is>
@@ -3604,7 +3613,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3634,7 +3643,7 @@
           <t>vo_ltr_ch</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>च</t>
         </is>
@@ -3655,7 +3664,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3685,7 +3694,7 @@
           <t>vo_ltr_l</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>ल</t>
         </is>
@@ -3706,7 +3715,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3736,7 +3745,7 @@
           <t>vo_ltr_r</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>र</t>
         </is>
@@ -3753,7 +3762,7 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3783,7 +3792,7 @@
           <t>vo_g3_correct</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए — इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
@@ -3800,7 +3809,7 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3830,7 +3839,7 @@
           <t>vo_g3_try</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>यह च की आवाज़ नहीं है।</t>
         </is>
@@ -3847,7 +3856,7 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3856,92 +3865,96 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Page 10</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Which sound came again?</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" t="n">
         <v>8</v>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>vo_g3_h1</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Hint 1</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>After the 1st wrong try</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Page 10</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Which sound came again?</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" t="n">
         <v>9</v>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>vo_g3_h3</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Hint 3</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>After the 3rd wrong try</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3980,7 @@
           <t>vo_g3_reveal</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>ध्यान से देखिए, सही जवाब च है।</t>
         </is>
@@ -4014,7 +4027,7 @@
           <t>vo_line_l6</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>नानी ने नई नाव बनाई।</t>
         </is>
@@ -4031,7 +4044,7 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4061,7 +4074,7 @@
           <t>vo_g3_prompt</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
         </is>
@@ -4082,7 +4095,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4112,7 +4125,7 @@
           <t>vo_ltr_n</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>न</t>
         </is>
@@ -4129,7 +4142,7 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4159,7 +4172,7 @@
           <t>vo_ltr_m</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>म</t>
         </is>
@@ -4180,7 +4193,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4210,7 +4223,7 @@
           <t>vo_ltr_l</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>ल</t>
         </is>
@@ -4231,7 +4244,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4261,7 +4274,7 @@
           <t>vo_p4_correct</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>सही! शुरुआत में न की आवाज़ थी।</t>
         </is>
@@ -4278,7 +4291,7 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4308,7 +4321,7 @@
           <t>vo_p4_try</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
@@ -4325,7 +4338,7 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4334,92 +4347,96 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Page 11</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Which sound came again?</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" t="n">
         <v>8</v>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>vo_p4_h1</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Hint 1</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>After the 1st wrong try</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Page 11</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Which sound came again?</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" t="n">
         <v>9</v>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>vo_p4_h3</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Hint 3</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>After the 3rd wrong try</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4462,7 @@
           <t>vo_p4_reveal</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
@@ -4462,7 +4479,7 @@
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>3.12</v>
+        <v>4.48</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4492,7 +4509,7 @@
           <t>vo_g5_prompt</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
         </is>
@@ -4509,7 +4526,7 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>6.92</v>
+        <v>4.28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4539,7 +4556,7 @@
           <t>vo_snd_p</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -4560,7 +4577,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4590,7 +4607,7 @@
           <t>vo_w_patang</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>पतंग</t>
         </is>
@@ -4611,7 +4628,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4641,7 +4658,7 @@
           <t>vo_w_chand</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>चाँद</t>
         </is>
@@ -4662,7 +4679,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4692,7 +4709,7 @@
           <t>vo_g5_correct</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>बहुत बढ़िया! सही डिब्बा।</t>
         </is>
@@ -4709,7 +4726,7 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4739,7 +4756,7 @@
           <t>vo_g5_prompt</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
         </is>
@@ -4756,7 +4773,7 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>6.92</v>
+        <v>4.28</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -4786,7 +4803,7 @@
           <t>vo_snd_p</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -4807,7 +4824,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -4837,7 +4854,7 @@
           <t>vo_g5_correct</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>बहुत बढ़िया! सही डिब्बा।</t>
         </is>
@@ -4854,7 +4871,7 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -4884,7 +4901,7 @@
           <t>vo_g5_try</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
         </is>
@@ -4901,7 +4918,7 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>4.84</v>
+        <v>4.4</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -4931,7 +4948,7 @@
           <t>vo_g5_hint</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
         </is>
@@ -4948,7 +4965,7 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>5.88</v>
+        <v>5.24</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -4957,47 +4974,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Page 12</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Sort into the right box - the child's turn</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" t="n">
         <v>6</v>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>vo_g5_h1</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Hint 1</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>After the 1st wrong try</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="3" t="inlineStr"/>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5042,7 @@
           <t>vo_pt_practice</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>(shared kit recording - already delivered, nothing to script or re-record)</t>
         </is>
@@ -5040,7 +5059,7 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5070,7 +5089,7 @@
           <t>vo_g1_prompt</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>प की आवाज़ वाले चित्र पर टैप कीजिए।</t>
         </is>
@@ -5087,7 +5106,7 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5117,7 +5136,7 @@
           <t>vo_snd_p</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -5138,7 +5157,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5168,7 +5187,7 @@
           <t>vo_w_patang</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>पतंग</t>
         </is>
@@ -5189,7 +5208,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5219,7 +5238,7 @@
           <t>vo_w_aam</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>आम</t>
         </is>
@@ -5240,7 +5259,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5270,7 +5289,7 @@
           <t>vo_w_papita</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>पपीता</t>
         </is>
@@ -5291,7 +5310,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5321,7 +5340,7 @@
           <t>vo_w_kela</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>केला</t>
         </is>
@@ -5342,7 +5361,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5372,7 +5391,7 @@
           <t>vo_w_patta</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>पत्ता</t>
         </is>
@@ -5419,7 +5438,7 @@
           <t>vo_w_ghar</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>घर</t>
         </is>
@@ -5436,7 +5455,7 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5466,7 +5485,7 @@
           <t>vo_w_pani</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>पानी</t>
         </is>
@@ -5483,7 +5502,7 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5513,7 +5532,7 @@
           <t>vo_w_machhli</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>मछली</t>
         </is>
@@ -5530,7 +5549,7 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5560,7 +5579,7 @@
           <t>vo_w_mala</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>माला</t>
         </is>
@@ -5581,7 +5600,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5611,7 +5630,7 @@
           <t>vo_w_muli</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>मूली</t>
         </is>
@@ -5632,7 +5651,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -5662,7 +5681,7 @@
           <t>vo_w_laal</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>लाल</t>
         </is>
@@ -5683,7 +5702,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -5713,7 +5732,7 @@
           <t>vo_w_chuha</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>चूहा</t>
         </is>
@@ -5734,7 +5753,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -5764,7 +5783,7 @@
           <t>vo_w_chand</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>चाँद</t>
         </is>
@@ -5785,7 +5804,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -5815,7 +5834,7 @@
           <t>vo_w_kauaa</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>कौआ</t>
         </is>
@@ -5862,7 +5881,7 @@
           <t>vo_w_chammach</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>चम्मच</t>
         </is>
@@ -5879,7 +5898,7 @@
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -5888,49 +5907,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Page 13</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Balloon game</t>
         </is>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="D116" t="n">
         <v>18</v>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>vo_w_kamal</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>कमल</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>the word «कमल» (round 2)</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>When that balloon is popped</t>
         </is>
       </c>
-      <c r="I116" s="3" t="inlineStr"/>
-      <c r="J116" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5975,7 @@
           <t>vo_w_chinti</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>चींटी</t>
         </is>
@@ -5973,7 +5992,7 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6003,7 +6022,7 @@
           <t>vo_w_kabutar</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>कबूतर</t>
         </is>
@@ -6050,7 +6069,7 @@
           <t>vo_g1_next</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>अब “च” की आवाज़ वाले चित्रों पर टैप कीजिए।</t>
         </is>
@@ -6067,7 +6086,7 @@
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6097,7 +6116,7 @@
           <t>vo_g1_correct2</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>शाबाश! इसमें च की आवाज़ है।</t>
         </is>
@@ -6114,7 +6133,7 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6144,7 +6163,7 @@
           <t>vo_g1_hint2</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>ध्यान से सुनिए, इसमें च की आवाज़ नहीं है।</t>
         </is>
@@ -6161,7 +6180,7 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
-        <v>6.32</v>
+        <v>4.32</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6191,7 +6210,7 @@
           <t>vo_g1_correct</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>शाबाश! इसमें प की आवाज़ है।</t>
         </is>
@@ -6208,7 +6227,7 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>1.64</v>
+        <v>3.88</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6238,7 +6257,7 @@
           <t>vo_g1_hint</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>ध्यान से सुनिए, इसमें प की आवाज़ नहीं है।</t>
         </is>
@@ -6255,7 +6274,7 @@
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>7.12</v>
+        <v>4.4</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6264,49 +6283,49 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Page 14</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Well done</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>vo_p8_prompt</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>page instruction</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>Page opens</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr"/>
-      <c r="J124" s="3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6362,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>94 distinct recordings. 20 still to record - those rows are highlighted.</t>
+          <t>94 distinct recordings. 0 still to record - those rows are highlighted.</t>
         </is>
       </c>
     </row>
@@ -6385,35 +6404,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>vo_landing</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>vo_landing.wav</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>नमस्ते दोस्तो! आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>SYNTHESISED - record a human take of the line in column D</t>
+      <c r="F5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6450,7 @@
           <t>vo_pt_tutorial.wav</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>(shared kit recording - already delivered, nothing to script or re-record)</t>
         </is>
@@ -6464,7 +6483,7 @@
           <t>vo_line_l2.wav</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>चूहे ने चार चने चबाए।</t>
         </is>
@@ -6475,7 +6494,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6497,7 +6516,7 @@
           <t>vo_ltr_ch.wav</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>च</t>
         </is>
@@ -6508,7 +6527,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6530,7 +6549,7 @@
           <t>vo_t3_explain.wav</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
@@ -6541,7 +6560,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6563,7 +6582,7 @@
           <t>vo_t4_prompt.wav</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
@@ -6574,7 +6593,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.72</v>
+        <v>6.64</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6596,7 +6615,7 @@
           <t>vo_w_chuha.wav</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>चूहा</t>
         </is>
@@ -6607,7 +6626,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6629,7 +6648,7 @@
           <t>vo_snd_ch.wav</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>च से चम्मच।</t>
         </is>
@@ -6640,7 +6659,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -6662,7 +6681,7 @@
           <t>vo_line_l3.wav</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>मेरे मामा मीठी मलाई लाए।</t>
         </is>
@@ -6673,7 +6692,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6695,7 +6714,7 @@
           <t>vo_ltr_m.wav</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>म</t>
         </is>
@@ -6706,7 +6725,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6728,7 +6747,7 @@
           <t>vo_t5_explain.wav</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
@@ -6739,7 +6758,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8.119999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6761,7 +6780,7 @@
           <t>vo_t6_prompt.wav</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
@@ -6772,7 +6791,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.72</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6794,7 +6813,7 @@
           <t>vo_w_muli.wav</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>मूली</t>
         </is>
@@ -6805,7 +6824,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6827,7 +6846,7 @@
           <t>vo_snd_m.wav</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>म से मछली।</t>
         </is>
@@ -6838,7 +6857,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6860,7 +6879,7 @@
           <t>vo_line_l1.wav</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>पीतल के पतीले में पपीता पीला-पीला।</t>
         </is>
@@ -6871,7 +6890,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6893,7 +6912,7 @@
           <t>vo_ltr_p.wav</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>प</t>
         </is>
@@ -6904,7 +6923,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.84</v>
+        <v>1.12</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6926,7 +6945,7 @@
           <t>vo_t1_explain.wav</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
@@ -6937,7 +6956,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8.56</v>
+        <v>8.68</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6959,7 +6978,7 @@
           <t>vo_t2_prompt.wav</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
@@ -6970,7 +6989,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7.56</v>
+        <v>7.28</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6992,7 +7011,7 @@
           <t>vo_w_papita.wav</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>पपीता</t>
         </is>
@@ -7003,7 +7022,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7025,7 +7044,7 @@
           <t>vo_snd_p.wav</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>प से पतंग।</t>
         </is>
@@ -7036,7 +7055,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7045,35 +7064,35 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>vo_g2_prompt</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>vo_g2_prompt.wav</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="F25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7110,7 @@
           <t>vo_w_kela.wav</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>केला</t>
         </is>
@@ -7102,7 +7121,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -7124,7 +7143,7 @@
           <t>vo_w_patang.wav</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>पतंग</t>
         </is>
@@ -7135,7 +7154,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -7157,7 +7176,7 @@
           <t>vo_w_aam.wav</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>आम</t>
         </is>
@@ -7168,7 +7187,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -7190,7 +7209,7 @@
           <t>vo_g2_more.wav</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>एक और प वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -7201,7 +7220,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -7223,7 +7242,7 @@
           <t>vo_g2_try.wav</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>इस शब्द की शुरुआत में प की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -7234,7 +7253,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.12</v>
+        <v>5.56</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -7256,7 +7275,7 @@
           <t>vo_g2_hint.wav</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>हर शब्द को ध्यान से देखिए और सुनिए। किस शब्द में प की आवाज़ आ रही है?</t>
         </is>
@@ -7267,7 +7286,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6.48</v>
+        <v>5.88</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -7276,95 +7295,101 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>vo_g2_h1</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>vo_g2_h1.wav</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F32" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>vo_g2_h2</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>vo_g2_h2.wav</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>vo_g2_h3</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>vo_g2_h3.wav</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F34" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7407,7 @@
           <t>vo_g2_reveal.wav</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें प की आवाज़ है।</t>
         </is>
@@ -7393,7 +7418,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -7415,7 +7440,7 @@
           <t>vo_g2_done.wav</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>शाबाश! तुमने प की आवाज़ वाले सारे शब्द खोज लिए।</t>
         </is>
@@ -7426,7 +7451,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5.24</v>
+        <v>5.56</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -7435,35 +7460,35 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>vo_p1_prompt</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>vo_p1_prompt.wav</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="F37" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7506,7 @@
           <t>vo_w_mama.wav</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>मामा</t>
         </is>
@@ -7514,7 +7539,7 @@
           <t>vo_w_chidiya.wav</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>चिड़िया</t>
         </is>
@@ -7525,7 +7550,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -7547,7 +7572,7 @@
           <t>vo_w_laddu.wav</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>लड्डू</t>
         </is>
@@ -7558,7 +7583,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -7580,7 +7605,7 @@
           <t>vo_p1_more.wav</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>एक और म वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -7591,7 +7616,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -7613,7 +7638,7 @@
           <t>vo_p1_try.wav</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -7624,7 +7649,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5.08</v>
+        <v>6.16</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -7646,7 +7671,7 @@
           <t>vo_p1_hint.wav</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
         </is>
@@ -7657,7 +7682,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4.96</v>
+        <v>4.48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7666,95 +7691,101 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>vo_p1_h1</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>vo_p1_h1.wav</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F44" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>vo_p1_h2</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>vo_p1_h2.wav</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F45" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>vo_p1_h3</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>vo_p1_h3.wav</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F46" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7803,7 @@
           <t>vo_p1_reveal.wav</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें म की आवाज़ है।</t>
         </is>
@@ -7783,7 +7814,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7805,7 +7836,7 @@
           <t>vo_p1_done.wav</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
         </is>
@@ -7816,7 +7847,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4.24</v>
+        <v>4.48</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7825,35 +7856,35 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>vo_p7_prompt</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>vo_p7_prompt.wav</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="F49" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7902,7 @@
           <t>vo_w_chand.wav</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>चाँद</t>
         </is>
@@ -7882,7 +7913,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7904,7 +7935,7 @@
           <t>vo_w_mala.wav</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>माला</t>
         </is>
@@ -7915,7 +7946,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -7937,7 +7968,7 @@
           <t>vo_w_chashma.wav</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>चश्मा</t>
         </is>
@@ -7970,7 +8001,7 @@
           <t>vo_w_laal.wav</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>लाल</t>
         </is>
@@ -7981,7 +8012,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8003,7 +8034,7 @@
           <t>vo_p7_more.wav</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
@@ -8014,7 +8045,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8036,7 +8067,7 @@
           <t>vo_p7_try.wav</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
@@ -8047,7 +8078,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>4.84</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8069,7 +8100,7 @@
           <t>vo_p7_hint.wav</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
@@ -8080,104 +8111,110 @@
         </is>
       </c>
       <c r="F56" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>vo_p7_h1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>vo_p7_h1.wav</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>6.28</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h1</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h1.wav</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>vo_p7_h2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>vo_p7_h2.wav</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h2</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h2.wav</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="F58" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>vo_p7_h3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>vo_p7_h3.wav</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h3</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>vo_p7_h3.wav</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F59" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8232,7 @@
           <t>vo_p7_reveal.wav</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
@@ -8206,7 +8243,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8228,7 +8265,7 @@
           <t>vo_p7_done.wav</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
@@ -8239,7 +8276,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -8261,7 +8298,7 @@
           <t>vo_g3_prompt.wav</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
         </is>
@@ -8272,7 +8309,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -8294,7 +8331,7 @@
           <t>vo_ltr_l.wav</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>ल</t>
         </is>
@@ -8305,7 +8342,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -8327,7 +8364,7 @@
           <t>vo_ltr_r.wav</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>र</t>
         </is>
@@ -8338,7 +8375,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8360,7 +8397,7 @@
           <t>vo_g3_correct.wav</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए — इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
@@ -8371,7 +8408,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8393,7 +8430,7 @@
           <t>vo_g3_try.wav</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>यह च की आवाज़ नहीं है।</t>
         </is>
@@ -8404,7 +8441,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8413,64 +8450,68 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>vo_g3_h1</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>vo_g3_h1.wav</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>vo_g3_h3</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>vo_g3_h3.wav</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F68" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8529,7 @@
           <t>vo_g3_reveal.wav</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>ध्यान से देखिए, सही जवाब च है।</t>
         </is>
@@ -8521,7 +8562,7 @@
           <t>vo_line_l6.wav</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>नानी ने नई नाव बनाई।</t>
         </is>
@@ -8532,7 +8573,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8554,7 +8595,7 @@
           <t>vo_ltr_n.wav</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>न</t>
         </is>
@@ -8565,7 +8606,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8587,7 +8628,7 @@
           <t>vo_p4_correct.wav</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>सही! शुरुआत में न की आवाज़ थी।</t>
         </is>
@@ -8598,7 +8639,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8620,7 +8661,7 @@
           <t>vo_p4_try.wav</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
@@ -8631,7 +8672,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8640,64 +8681,68 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>vo_p4_h1</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>vo_p4_h1.wav</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>vo_p4_h3</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>vo_p4_h3.wav</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>p11</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F75" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8760,7 @@
           <t>vo_p4_reveal.wav</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
@@ -8726,7 +8771,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.12</v>
+        <v>4.48</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -8748,7 +8793,7 @@
           <t>vo_g5_prompt.wav</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
         </is>
@@ -8759,7 +8804,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6.92</v>
+        <v>4.28</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -8781,7 +8826,7 @@
           <t>vo_g5_correct.wav</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>बहुत बढ़िया! सही डिब्बा।</t>
         </is>
@@ -8792,7 +8837,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -8814,7 +8859,7 @@
           <t>vo_g5_try.wav</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
         </is>
@@ -8825,7 +8870,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4.84</v>
+        <v>4.4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -8847,7 +8892,7 @@
           <t>vo_g5_hint.wav</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
         </is>
@@ -8858,7 +8903,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>5.88</v>
+        <v>5.24</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8867,33 +8912,35 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>vo_g5_h1</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>vo_g5_h1.wav</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>p12</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+      <c r="F81" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8958,7 @@
           <t>vo_pt_practice.wav</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>(shared kit recording - already delivered, nothing to script or re-record)</t>
         </is>
@@ -8922,7 +8969,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -8944,7 +8991,7 @@
           <t>vo_g1_prompt.wav</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>प की आवाज़ वाले चित्र पर टैप कीजिए।</t>
         </is>
@@ -8955,7 +9002,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -8977,7 +9024,7 @@
           <t>vo_w_patta.wav</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>पत्ता</t>
         </is>
@@ -9010,7 +9057,7 @@
           <t>vo_w_ghar.wav</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>घर</t>
         </is>
@@ -9021,7 +9068,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -9043,7 +9090,7 @@
           <t>vo_w_pani.wav</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>पानी</t>
         </is>
@@ -9054,7 +9101,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -9076,7 +9123,7 @@
           <t>vo_w_machhli.wav</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>मछली</t>
         </is>
@@ -9087,7 +9134,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -9109,7 +9156,7 @@
           <t>vo_w_kauaa.wav</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>कौआ</t>
         </is>
@@ -9142,7 +9189,7 @@
           <t>vo_w_chammach.wav</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>चम्मच</t>
         </is>
@@ -9153,7 +9200,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -9162,35 +9209,35 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>vo_w_kamal</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>vo_w_kamal.wav</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>कमल</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>p13</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="F90" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9255,7 @@
           <t>vo_w_chinti.wav</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>चींटी</t>
         </is>
@@ -9219,7 +9266,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -9241,7 +9288,7 @@
           <t>vo_w_kabutar.wav</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>कबूतर</t>
         </is>
@@ -9274,7 +9321,7 @@
           <t>vo_g1_next.wav</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>अब “च” की आवाज़ वाले चित्रों पर टैप कीजिए।</t>
         </is>
@@ -9285,7 +9332,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -9307,7 +9354,7 @@
           <t>vo_g1_correct2.wav</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>शाबाश! इसमें च की आवाज़ है।</t>
         </is>
@@ -9318,7 +9365,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -9340,7 +9387,7 @@
           <t>vo_g1_hint2.wav</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>ध्यान से सुनिए, इसमें च की आवाज़ नहीं है।</t>
         </is>
@@ -9351,7 +9398,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>6.32</v>
+        <v>4.32</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -9373,7 +9420,7 @@
           <t>vo_g1_correct.wav</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>शाबाश! इसमें प की आवाज़ है।</t>
         </is>
@@ -9384,7 +9431,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1.64</v>
+        <v>3.88</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -9406,7 +9453,7 @@
           <t>vo_g1_hint.wav</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>ध्यान से सुनिए, इसमें प की आवाज़ नहीं है।</t>
         </is>
@@ -9417,7 +9464,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>7.12</v>
+        <v>4.4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -9426,35 +9473,35 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>vo_p8_prompt</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>vo_p8_prompt.wav</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>p14</t>
         </is>
       </c>
-      <c r="F98" s="3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+      <c r="F98" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9823,7 @@
           <t>Scope</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>The whole lesson - start screen, 2 transitions, 14 pages, celebration. The balloon game's words are in here too; it has no separate manifest.</t>
         </is>
@@ -9788,7 +9835,7 @@
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Game order. On each page: what plays as it opens, then the board's own clips, then the correct answer, then the 1st / 2nd / 3rd wrong try (Hint 1, 2, 3), then the closing line. Hints only sound after a wrong answer, so that part is the order they would be reached in, not a guarantee they are all heard.</t>
         </is>
@@ -9800,9 +9847,9 @@
           <t>Clips</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>120 rows, 94 distinct recordings (see 'Recording list'). 20 still to record.</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>120 rows, 94 distinct recordings (see 'Recording list'). 0 still to record.</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9859,7 @@
           <t>Deliver to</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>A flat folder named &lt;Audio ID&gt;.wav - the file name IS the Audio ID. intake_vo.py renames into build/assets/Audio/ and the build encodes Opus 28k mono for the delivery; do not send .ogg or .mp3.</t>
         </is>
@@ -9824,7 +9871,7 @@
           <t>Voice</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>HUMAN, one narrator, warm and unhurried for Grade 2. This lesson does not use TTS and has no TTS fallback - a missing clip is silent on purpose, so that a gap is noticed rather than papered over by a robot voice.</t>
         </is>
@@ -9836,7 +9883,7 @@
           <t>Format</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>WAV, 16-bit PCM, MONO, 48 kHz. 16-bit is a hard requirement, not a preference: the word-by-word highlighting is timed by reading the waveform and that reader only understands 16-bit PCM WAV. No added silence, no fades, no music bed, no brickwall normalisation.</t>
         </is>
@@ -9848,7 +9895,7 @@
           <t>Register</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>आप form throughout - सुनिए, कीजिए, डालिए. The closing line uses तुम, which is the standard end-screen dialogue and the one allowed exception.</t>
         </is>
@@ -9860,7 +9907,7 @@
           <t>Script</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Record exactly the text in the Hindi script column - it is the build's own text, and the on-screen wording is generated from the same source.</t>
         </is>
@@ -9872,7 +9919,7 @@
           <t>Bare sounds</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>vo_snd_p / vo_snd_ch / vo_snd_m are a bare letter sound followed by one example word. They are SHORT on purpose and the build guards them - do not pad them into a sentence.</t>
         </is>
@@ -9884,7 +9931,7 @@
           <t>After vo_p8_prompt</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>If the closing line is re-recorded, re-run _assets_round4/make_lipsync.py. Swiftie's mouth on the end screen is driven by a track measured from that exact clip; a new take without it leaves her lip-sync running to the old rhythm.</t>
         </is>
@@ -9896,7 +9943,7 @@
           <t>Re-recording</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Keep the same file name; the build re-stamps the audio so the new take reaches browsers.</t>
         </is>
@@ -9908,7 +9955,7 @@
           <t>Regenerate</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>PYTHONUTF8=1 python gen_lesson_vo_manifest.py</t>
         </is>
